--- a/events/Poznan_2013_WC/Poznan_2013_WC_Results.xlsx
+++ b/events/Poznan_2013_WC/Poznan_2013_WC_Results.xlsx
@@ -2397,6 +2397,11 @@
           <t>46100</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>118912</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3177,6 +3182,11 @@
           <t>4:12.394</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3367,6 +3377,11 @@
           <t>4:07.095</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3927,6 +3942,11 @@
           <t>4:04.781</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3987,6 +4007,11 @@
           <t>4:05.145</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5982,6 +6007,11 @@
           <t>3:51.930</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>42488</t>
@@ -6847,6 +6877,11 @@
           <t>4:08.462</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6907,6 +6942,11 @@
           <t>4:23.678</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>36005</t>
@@ -6972,6 +7012,11 @@
           <t>4:24.914</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>45118</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7102,6 +7147,16 @@
           <t>4:07.877</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7802,6 +7857,11 @@
           <t>56241</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>42452</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7862,6 +7922,16 @@
           <t>3:24.818</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>42131</t>
+        </is>
+      </c>
       <c r="T114" t="inlineStr">
         <is>
           <t>42128</t>
@@ -7942,6 +8012,11 @@
           <t>42731</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8092,6 +8167,11 @@
           <t>56336</t>
         </is>
       </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8232,6 +8312,11 @@
           <t>52102</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>52103</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9755,6 +9840,11 @@
           <t>46100</t>
         </is>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>118912</t>
+        </is>
+      </c>
       <c r="X143" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -9820,6 +9910,11 @@
           <t>3:49.574</t>
         </is>
       </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10260,6 +10355,11 @@
           <t>3:56.086</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12235,6 +12335,11 @@
           <t>3:33.608</t>
         </is>
       </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>42488</t>
@@ -12770,6 +12875,11 @@
           <t>3:59.317</t>
         </is>
       </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12830,6 +12940,11 @@
           <t>3:59.373</t>
         </is>
       </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>36005</t>
@@ -13035,6 +13150,11 @@
           <t>4:30.421</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>45118</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13175,6 +13295,11 @@
           <t>56241</t>
         </is>
       </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>42452</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13235,6 +13360,16 @@
           <t>3:16.351</t>
         </is>
       </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>42131</t>
+        </is>
+      </c>
       <c r="T197" t="inlineStr">
         <is>
           <t>42128</t>
@@ -13310,6 +13445,11 @@
           <t>52102</t>
         </is>
       </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>52103</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13890,6 +14030,11 @@
           <t>1:46.511</t>
         </is>
       </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14145,6 +14290,11 @@
           <t>1:48.911</t>
         </is>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15400,6 +15550,11 @@
           <t>1:59.991</t>
         </is>
       </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -17079,6 +17234,11 @@
           <t>1:41.190</t>
         </is>
       </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>42128</t>
@@ -17144,6 +17304,11 @@
           <t>1:41.794</t>
         </is>
       </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>42488</t>
@@ -18159,6 +18324,11 @@
           <t>47674</t>
         </is>
       </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -18219,6 +18389,11 @@
           <t>1:56.899</t>
         </is>
       </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -18349,6 +18524,11 @@
           <t>2:06.435</t>
         </is>
       </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>45118</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -18409,6 +18589,16 @@
           <t>1:47.254</t>
         </is>
       </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -18869,6 +19059,11 @@
           <t>1:43.937</t>
         </is>
       </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -20399,6 +20594,11 @@
           <t>1:50.163</t>
         </is>
       </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -20713,6 +20913,11 @@
           <t>1:57.993</t>
         </is>
       </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -21488,6 +21693,11 @@
           <t>1:37.995</t>
         </is>
       </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S325" t="inlineStr">
         <is>
           <t>42488</t>
@@ -22288,6 +22498,11 @@
           <t>1:47.941</t>
         </is>
       </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
       <c r="S337" t="inlineStr">
         <is>
           <t>42128</t>
@@ -22683,6 +22898,11 @@
           <t>47674</t>
         </is>
       </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -22743,6 +22963,11 @@
           <t>1:54.106</t>
         </is>
       </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -22862,6 +23087,11 @@
       <c r="L346" t="n">
         <v>9</v>
       </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>45118</t>
+        </is>
+      </c>
       <c r="X346" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -26032,6 +26262,11 @@
           <t>3:35.396</t>
         </is>
       </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -26094,6 +26329,11 @@
           <t>3:36.884</t>
         </is>
       </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -26156,6 +26396,11 @@
           <t>3:37.016</t>
         </is>
       </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -27779,6 +28024,16 @@
           <t>3:44.005</t>
         </is>
       </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -28263,6 +28518,11 @@
           <t>3:52.729</t>
         </is>
       </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -29556,6 +29816,11 @@
           <t>56241</t>
         </is>
       </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>42452</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -29705,6 +29970,11 @@
           <t>42731</t>
         </is>
       </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -29777,6 +30047,11 @@
           <t>56336</t>
         </is>
       </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -29978,6 +30253,16 @@
           <t>3:11.716</t>
         </is>
       </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>42131</t>
+        </is>
+      </c>
       <c r="T452" t="inlineStr">
         <is>
           <t>42128</t>
@@ -30291,6 +30576,11 @@
           <t>47674</t>
         </is>
       </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -30713,6 +31003,11 @@
           <t>0:37.404</t>
         </is>
       </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -30893,6 +31188,11 @@
           <t>0:39.272</t>
         </is>
       </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>52103</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -31318,6 +31618,11 @@
           <t>0:37.892</t>
         </is>
       </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>42538</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -31753,6 +32058,11 @@
           <t>0:38.342</t>
         </is>
       </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>94131</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -33388,6 +33698,11 @@
           <t>0:41.734</t>
         </is>
       </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -35443,6 +35758,11 @@
           <t>42171</t>
         </is>
       </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -36718,6 +37038,11 @@
           <t>42151</t>
         </is>
       </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -36838,6 +37163,11 @@
           <t>0:42.115</t>
         </is>
       </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>45118</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -37808,6 +38138,11 @@
           <t>0:52.178</t>
         </is>
       </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>36173</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -38363,6 +38698,11 @@
           <t>0:37.722</t>
         </is>
       </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -38483,6 +38823,11 @@
           <t>0:38.646</t>
         </is>
       </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>94131</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -39038,6 +39383,11 @@
           <t>0:38.028</t>
         </is>
       </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>42538</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -39163,6 +39513,11 @@
           <t>0:39.092</t>
         </is>
       </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>52103</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -42408,6 +42763,11 @@
           <t>42171</t>
         </is>
       </c>
+      <c r="S646" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -43538,6 +43898,11 @@
           <t>0:42.830</t>
         </is>
       </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>45118</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -44810,6 +45175,11 @@
           <t>0:39.158</t>
         </is>
       </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>42538</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -45001,6 +45371,11 @@
           <t>0:39.342</t>
         </is>
       </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>94131</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -46929,6 +47304,11 @@
           <t>42171</t>
         </is>
       </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -47057,6 +47437,11 @@
           <t>1:38.898</t>
         </is>
       </c>
+      <c r="S717" t="inlineStr">
+        <is>
+          <t>36670</t>
+        </is>
+      </c>
       <c r="U717" t="inlineStr">
         <is>
           <t>35700</t>
@@ -47494,6 +47879,21 @@
           <t>1:46.726</t>
         </is>
       </c>
+      <c r="R723" t="inlineStr">
+        <is>
+          <t>42661</t>
+        </is>
+      </c>
+      <c r="S723" t="inlineStr">
+        <is>
+          <t>42662</t>
+        </is>
+      </c>
+      <c r="U723" t="inlineStr">
+        <is>
+          <t>42663</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -47556,6 +47956,11 @@
           <t>1:47.910</t>
         </is>
       </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>42542</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -48216,6 +48621,11 @@
           <t>1:53.746</t>
         </is>
       </c>
+      <c r="R734" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -48670,6 +49080,11 @@
           <t>2:01.970</t>
         </is>
       </c>
+      <c r="R741" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -49196,6 +49611,11 @@
           <t>0:37.967</t>
         </is>
       </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -49578,6 +49998,11 @@
           <t>0:43.154</t>
         </is>
       </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -51814,6 +52239,11 @@
           <t>42151</t>
         </is>
       </c>
+      <c r="S788" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -52561,6 +52991,11 @@
           <t>0:54.200</t>
         </is>
       </c>
+      <c r="R799" t="inlineStr">
+        <is>
+          <t>36173</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -53211,6 +53646,11 @@
           <t>1:40.396</t>
         </is>
       </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S809" t="inlineStr">
         <is>
           <t>42488</t>
@@ -54298,6 +54738,16 @@
           <t>1:47.476</t>
         </is>
       </c>
+      <c r="R825" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S825" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -55730,6 +56180,11 @@
           <t>23:54.882</t>
         </is>
       </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -57051,6 +57506,11 @@
           <t>19:50.998</t>
         </is>
       </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -57113,6 +57573,11 @@
           <t>19:51.574</t>
         </is>
       </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -57706,6 +58171,11 @@
           <t>20:45.570</t>
         </is>
       </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -58393,6 +58863,11 @@
       </c>
       <c r="L888" t="n">
         <v>5</v>
+      </c>
+      <c r="R888" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
       </c>
       <c r="X888" t="inlineStr">
         <is>
@@ -58523,7 +58998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D189"/>
+  <dimension ref="A1:D216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62684,6 +63159,600 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Ilya</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>PERVUKHIN</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Alexey</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>KOROVASHKOV</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>36173</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>KAZAKOVA</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>36670</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Verena</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>HANTL</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Jesus</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>42131</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>42452</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Philippe</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>DUCHESNEAU</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Yul</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>OELTZE</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>42538</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Franck</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>LE MOEL</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>42542</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Lea</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>CAURANT</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>42661</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>BRUSKA</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>42662</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Aleksandra</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>GORNA</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>42663</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Martyna</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>LISIECKA</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Nelson Roberto</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>GERINGER SALLETE</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>FITZSIMON</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>45118</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Taras</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>MATVIICHUK</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Robert Michael James</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>CLARKE</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>52103</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Johan</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>LILJA</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Aleksey</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>MOCHALOV</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Nurislom</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>TUKHTASIN UGLI</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>94131</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>David James</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>GERBER</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SITKOWSKI</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>118912</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Jeanarett</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Oleg</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SHELEGOV</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2013_WC/Poznan_2013_WC_Results.xlsx
+++ b/events/Poznan_2013_WC/Poznan_2013_WC_Results.xlsx
@@ -15360,6 +15360,11 @@
           <t>1:58.715</t>
         </is>
       </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -33258,6 +33263,11 @@
           <t>0:41.838</t>
         </is>
       </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -49018,6 +49028,11 @@
           <t>2:01.502</t>
         </is>
       </c>
+      <c r="R740" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -50388,6 +50403,11 @@
       <c r="P761" t="inlineStr">
         <is>
           <t>0:47.926</t>
+        </is>
+      </c>
+      <c r="R761" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -58998,7 +59018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D216"/>
+  <dimension ref="A1:D217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63753,6 +63773,28 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>NIVALTER</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>DE JESUS</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
